--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0ae25cf28fa736a/Projects/BIAutomations/shipment-schedule/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12D8FCBA-D29A-4452-A689-9D797CD12333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D433F8B7-B0F4-469C-8EBE-E3B02AA34448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D6A6025-8B1B-48A3-8E45-59F8B6ED788E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02E18CEB-23E1-4EBC-BBED-A2AB2810F314}"/>
   </bookViews>
   <sheets>
     <sheet name="OPTSensiMedicalSalesOpenOrderR" sheetId="1" r:id="rId1"/>
@@ -1812,7 +1812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DB573A-D95A-4425-85CE-862B7B22548E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC46150-326D-42C1-BB96-165D0567BD85}">
   <dimension ref="A1:Z68"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <sheetData>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0ae25cf28fa736a/Projects/BIAutomations/shipment-schedule/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A5DE2CA-E924-4338-91FF-DC616A170D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51E722FE-2CF0-4882-AFFA-370AD094DF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D121D171-449F-4A23-8121-1D6419428C54}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00CF2670-F063-4D63-88E8-7977E8C1D688}"/>
   </bookViews>
   <sheets>
     <sheet name="OPTSensiMedicalSalesOpenOrderR" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="280">
   <si>
     <t>Division</t>
   </si>
@@ -100,6 +100,189 @@
     <t>Shipping Zip</t>
   </si>
   <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>202033</t>
+  </si>
+  <si>
+    <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+  </si>
+  <si>
+    <t>SO153640</t>
+  </si>
+  <si>
+    <t>4519692670</t>
+  </si>
+  <si>
+    <t>SENSI MEDICAL</t>
+  </si>
+  <si>
+    <t>V7871800000</t>
+  </si>
+  <si>
+    <t>20164396C</t>
+  </si>
+  <si>
+    <t>O-T7871800000</t>
+  </si>
+  <si>
+    <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1040 ENTERPRISE PARKWAY</t>
+  </si>
+  <si>
+    <t>WEST JEFFERSON</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>43162</t>
+  </si>
+  <si>
+    <t>209304</t>
+  </si>
+  <si>
+    <t>RGH Enterprises, Inc. dba Cardinal Health At-Home 209304</t>
+  </si>
+  <si>
+    <t>SO153643</t>
+  </si>
+  <si>
+    <t>1042653452</t>
+  </si>
+  <si>
+    <t>7871800000</t>
+  </si>
+  <si>
+    <t>20164394C</t>
+  </si>
+  <si>
+    <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+  </si>
+  <si>
+    <t>1810 Summit Commerce Pkwy</t>
+  </si>
+  <si>
+    <t>Twinsburg</t>
+  </si>
+  <si>
+    <t>44087</t>
+  </si>
+  <si>
+    <t>202040</t>
+  </si>
+  <si>
+    <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
+  </si>
+  <si>
+    <t>SO153650</t>
+  </si>
+  <si>
+    <t>3584739</t>
+  </si>
+  <si>
+    <t>V7871800002</t>
+  </si>
+  <si>
+    <t>20164397C</t>
+  </si>
+  <si>
+    <t>354866</t>
+  </si>
+  <si>
+    <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+  </si>
+  <si>
+    <t>500 INDUSTRIAL PARK DRIVE</t>
+  </si>
+  <si>
+    <t>SHELBYVILLE</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>46176</t>
+  </si>
+  <si>
+    <t>SO153651</t>
+  </si>
+  <si>
+    <t>3584740</t>
+  </si>
+  <si>
+    <t>1473 MOUNTAIN ROAD</t>
+  </si>
+  <si>
+    <t>ANDERSONVILLE</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>37705</t>
+  </si>
+  <si>
+    <t>SO153649</t>
+  </si>
+  <si>
+    <t>3584738</t>
+  </si>
+  <si>
+    <t>7871800002</t>
+  </si>
+  <si>
+    <t>20164395C</t>
+  </si>
+  <si>
+    <t>354862</t>
+  </si>
+  <si>
+    <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+  </si>
+  <si>
+    <t>276 ENTERPRISE WAY</t>
+  </si>
+  <si>
+    <t>MOCKSVILLE</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>27028</t>
+  </si>
+  <si>
+    <t>SO153652</t>
+  </si>
+  <si>
+    <t>3584741</t>
+  </si>
+  <si>
+    <t>354864</t>
+  </si>
+  <si>
+    <t>3625 PARK CIRCLE DRIVE</t>
+  </si>
+  <si>
+    <t>KALAMAZOO</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>49048</t>
+  </si>
+  <si>
     <t>ASV</t>
   </si>
   <si>
@@ -115,81 +298,21 @@
     <t>B1310223595-10</t>
   </si>
   <si>
-    <t>SENSI MEDICAL</t>
-  </si>
-  <si>
-    <t>7871800000</t>
-  </si>
-  <si>
-    <t>20164394C</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
     <t>1033 COLLINS RD STE A</t>
   </si>
   <si>
     <t>Greenwood</t>
   </si>
   <si>
-    <t>IN</t>
-  </si>
-  <si>
     <t>46143</t>
   </si>
   <si>
-    <t>SO153452</t>
-  </si>
-  <si>
-    <t>B1210223594-10</t>
-  </si>
-  <si>
-    <t>1605 Zeager Rd, Ste 101</t>
-  </si>
-  <si>
-    <t>Elizabethtown</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>17022</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>202033</t>
-  </si>
-  <si>
-    <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
-  </si>
-  <si>
     <t>SO153478</t>
   </si>
   <si>
     <t>4519685454</t>
   </si>
   <si>
-    <t>V7871800000</t>
-  </si>
-  <si>
-    <t>20164396C</t>
-  </si>
-  <si>
-    <t>O-T7871800000</t>
-  </si>
-  <si>
-    <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
-  </si>
-  <si>
     <t>21111 E. 36TH DRIVE</t>
   </si>
   <si>
@@ -220,48 +343,18 @@
     <t>60030</t>
   </si>
   <si>
-    <t>7871800002</t>
-  </si>
-  <si>
-    <t>20164395C</t>
-  </si>
-  <si>
     <t>O-T7871800002</t>
   </si>
   <si>
-    <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
-  </si>
-  <si>
-    <t>V7871800002</t>
-  </si>
-  <si>
-    <t>20164397C</t>
-  </si>
-  <si>
     <t>O-T871800002</t>
   </si>
   <si>
-    <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
-  </si>
-  <si>
     <t>SO153498</t>
   </si>
   <si>
     <t>4519685473</t>
   </si>
   <si>
-    <t>1040 ENTERPRISE PARKWAY</t>
-  </si>
-  <si>
-    <t>WEST JEFFERSON</t>
-  </si>
-  <si>
-    <t>OH</t>
-  </si>
-  <si>
-    <t>43162</t>
-  </si>
-  <si>
     <t>SO153506</t>
   </si>
   <si>
@@ -382,9 +475,6 @@
     <t>ROMULUS</t>
   </si>
   <si>
-    <t>MI</t>
-  </si>
-  <si>
     <t>48174</t>
   </si>
   <si>
@@ -508,9 +598,6 @@
     <t>MOUNT JULIET</t>
   </si>
   <si>
-    <t>TN</t>
-  </si>
-  <si>
     <t>37122</t>
   </si>
   <si>
@@ -769,25 +856,10 @@
     <t>21226</t>
   </si>
   <si>
-    <t>209304</t>
-  </si>
-  <si>
-    <t>RGH Enterprises, Inc. dba Cardinal Health At-Home 209304</t>
-  </si>
-  <si>
     <t>SO153164</t>
   </si>
   <si>
     <t>1042370490</t>
-  </si>
-  <si>
-    <t>1810 Summit Commerce Pkwy</t>
-  </si>
-  <si>
-    <t>Twinsburg</t>
-  </si>
-  <si>
-    <t>44087</t>
   </si>
 </sst>
 </file>
@@ -1659,8 +1731,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C24BC94-6DC9-45B6-9674-73EB62CFB408}">
-  <dimension ref="A1:Z51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A9AD0A-6999-4E54-A9B7-894575801D50}">
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -1748,7 +1820,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -1781,16 +1853,16 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>1794</v>
+        <v>18525</v>
       </c>
       <c r="N2">
-        <v>1777</v>
+        <v>18499</v>
       </c>
       <c r="O2">
-        <v>8</v>
-      </c>
-      <c r="P2">
-        <v>8</v>
+        <v>80</v>
+      </c>
+      <c r="P2" t="s">
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1805,22 +1877,22 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V2">
-        <v>57.33</v>
+        <v>47.46</v>
       </c>
       <c r="W2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Y2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
@@ -1828,49 +1900,49 @@
         <v>26</v>
       </c>
       <c r="B3" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
         <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L3" t="s">
         <v>36</v>
       </c>
       <c r="M3">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="N3">
         <v>1777</v>
       </c>
       <c r="O3">
-        <v>3</v>
-      </c>
-      <c r="P3">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1885,72 +1957,72 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="V3">
         <v>57.33</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="X3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Y3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="Z3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
         <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
       </c>
       <c r="M4">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N4">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O4">
-        <v>130</v>
-      </c>
-      <c r="P4" t="s">
-        <v>34</v>
+        <v>15</v>
+      </c>
+      <c r="P4">
+        <v>15</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1965,72 +2037,72 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="X4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="Y4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Z4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
         <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L5" t="s">
         <v>36</v>
       </c>
       <c r="M5">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N5">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O5">
-        <v>28</v>
-      </c>
-      <c r="P5" t="s">
-        <v>34</v>
+        <v>14</v>
+      </c>
+      <c r="P5">
+        <v>14</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2045,72 +2117,72 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="X5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Y5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L6" t="s">
         <v>36</v>
       </c>
       <c r="M6">
-        <v>8456</v>
+        <v>12656</v>
       </c>
       <c r="N6">
-        <v>8406</v>
+        <v>12550</v>
       </c>
       <c r="O6">
-        <v>34</v>
-      </c>
-      <c r="P6" t="s">
-        <v>34</v>
+        <v>56</v>
+      </c>
+      <c r="P6">
+        <v>56</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2125,72 +2197,72 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <v>36.86</v>
       </c>
       <c r="W6" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="X6" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="Y6" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="Z6" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>
       </c>
       <c r="M7">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N7">
-        <v>37803</v>
+        <v>18499</v>
       </c>
       <c r="O7">
-        <v>70</v>
-      </c>
-      <c r="P7" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="P7">
+        <v>26</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2205,72 +2277,72 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W7" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="X7" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="Y7" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L8" t="s">
         <v>36</v>
       </c>
       <c r="M8">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N8">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O8">
-        <v>13</v>
-      </c>
-      <c r="P8" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="P8">
+        <v>26</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2285,72 +2357,72 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W8" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="X8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Y8" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="Z8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B9" s="2">
         <v>46086</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L9" t="s">
         <v>36</v>
       </c>
       <c r="M9">
-        <v>18525</v>
+        <v>1791</v>
       </c>
       <c r="N9">
-        <v>18525</v>
+        <v>1777</v>
       </c>
       <c r="O9">
-        <v>27</v>
-      </c>
-      <c r="P9" t="s">
-        <v>34</v>
+        <v>8</v>
+      </c>
+      <c r="P9">
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2365,72 +2437,72 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="X9" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="Y9" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="Z9" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2">
         <v>46086</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G10" t="s">
         <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L10" t="s">
         <v>36</v>
       </c>
       <c r="M10">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N10">
-        <v>37803</v>
+        <v>18499</v>
       </c>
       <c r="O10">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2445,57 +2517,57 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="V10">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W10" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="X10" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="Y10" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="Z10" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2">
         <v>46086</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G11" t="s">
         <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J11" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="K11" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L11" t="s">
         <v>36</v>
@@ -2504,13 +2576,13 @@
         <v>18525</v>
       </c>
       <c r="N11">
-        <v>18525</v>
+        <v>18499</v>
       </c>
       <c r="O11">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2525,152 +2597,152 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="V11">
         <v>47.46</v>
       </c>
       <c r="W11" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="X11" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="Y11" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="Z11" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2">
         <v>46086</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G12" t="s">
         <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J12" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="K12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L12" t="s">
         <v>36</v>
       </c>
       <c r="M12">
-        <v>37803</v>
+        <v>12656</v>
       </c>
       <c r="N12">
-        <v>37803</v>
+        <v>12550</v>
       </c>
       <c r="O12">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="P12" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
         <v>34</v>
       </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>70</v>
-      </c>
       <c r="V12">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W12" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="X12" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="Y12" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="Z12" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2">
         <v>46086</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G13" t="s">
         <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J13" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L13" t="s">
         <v>36</v>
       </c>
       <c r="M13">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N13">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O13">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2685,72 +2757,72 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="V13">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W13" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="X13" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="Y13" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="Z13" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2">
         <v>46086</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G14" t="s">
         <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J14" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="K14" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L14" t="s">
         <v>36</v>
       </c>
       <c r="M14">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N14">
-        <v>37803</v>
+        <v>18499</v>
       </c>
       <c r="O14">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2765,57 +2837,57 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="V14">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W14" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="X14" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="Y14" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="Z14" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2">
         <v>46086</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F15" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G15" t="s">
         <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I15" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J15" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="K15" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L15" t="s">
         <v>36</v>
@@ -2824,13 +2896,13 @@
         <v>18525</v>
       </c>
       <c r="N15">
-        <v>18525</v>
+        <v>18499</v>
       </c>
       <c r="O15">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="P15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2845,72 +2917,72 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="V15">
         <v>47.46</v>
       </c>
       <c r="W15" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="X15" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Y15" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="Z15" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2">
         <v>46086</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F16" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G16" t="s">
         <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I16" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="K16" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L16" t="s">
         <v>36</v>
       </c>
       <c r="M16">
-        <v>8456</v>
+        <v>37803</v>
       </c>
       <c r="N16">
-        <v>8406</v>
+        <v>37748</v>
       </c>
       <c r="O16">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2925,72 +2997,72 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="V16">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W16" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="X16" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Y16" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="Z16" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2">
         <v>46086</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="G17" t="s">
         <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I17" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J17" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="K17" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L17" t="s">
         <v>36</v>
       </c>
       <c r="M17">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N17">
-        <v>37803</v>
+        <v>18499</v>
       </c>
       <c r="O17">
         <v>18</v>
       </c>
       <c r="P17" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3008,69 +3080,69 @@
         <v>18</v>
       </c>
       <c r="V17">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W17" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="X17" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="Y17" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="Z17" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2">
         <v>46086</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G18" t="s">
         <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J18" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="K18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L18" t="s">
         <v>36</v>
       </c>
       <c r="M18">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N18">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O18">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3085,72 +3157,72 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="V18">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W18" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="X18" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="Y18" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="Z18" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
         <v>46086</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F19" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G19" t="s">
         <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="J19" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="K19" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="L19" t="s">
         <v>36</v>
       </c>
       <c r="M19">
-        <v>8456</v>
+        <v>18525</v>
       </c>
       <c r="N19">
-        <v>8406</v>
+        <v>18499</v>
       </c>
       <c r="O19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3165,57 +3237,57 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="V19">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W19" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="X19" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="Y19" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="Z19" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2">
         <v>46086</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="F20" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="G20" t="s">
         <v>31</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I20" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J20" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K20" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L20" t="s">
         <v>36</v>
@@ -3224,13 +3296,13 @@
         <v>37803</v>
       </c>
       <c r="N20">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="O20">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="P20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3245,72 +3317,72 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="V20">
         <v>29.4</v>
       </c>
       <c r="W20" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="X20" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="Y20" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="Z20" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2">
         <v>46086</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="G21" t="s">
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I21" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="J21" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="K21" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="L21" t="s">
         <v>36</v>
       </c>
       <c r="M21">
-        <v>8456</v>
+        <v>18525</v>
       </c>
       <c r="N21">
-        <v>8406</v>
+        <v>18499</v>
       </c>
       <c r="O21">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3325,72 +3397,72 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="V21">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W21" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="X21" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="Y21" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="Z21" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B22" s="2">
         <v>46086</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F22" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="G22" t="s">
         <v>31</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="I22" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="K22" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="L22" t="s">
         <v>36</v>
       </c>
       <c r="M22">
-        <v>18525</v>
+        <v>12656</v>
       </c>
       <c r="N22">
-        <v>18525</v>
+        <v>12550</v>
       </c>
       <c r="O22">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3405,57 +3477,57 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="V22">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W22" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="X22" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="Y22" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="Z22" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B23" s="2">
         <v>46086</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F23" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="G23" t="s">
         <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I23" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J23" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K23" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L23" t="s">
         <v>36</v>
@@ -3464,13 +3536,13 @@
         <v>37803</v>
       </c>
       <c r="N23">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="O23">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -3485,72 +3557,72 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="V23">
         <v>29.4</v>
       </c>
       <c r="W23" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="X23" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="Y23" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="Z23" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2">
         <v>46086</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="F24" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G24" t="s">
         <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I24" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J24" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="K24" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L24" t="s">
         <v>36</v>
       </c>
       <c r="M24">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N24">
-        <v>37803</v>
+        <v>18499</v>
       </c>
       <c r="O24">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="P24" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -3565,72 +3637,72 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W24" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="X24" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="Y24" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="Z24" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B25" s="2">
         <v>46086</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F25" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G25" t="s">
         <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I25" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="K25" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L25" t="s">
         <v>36</v>
       </c>
       <c r="M25">
-        <v>8456</v>
+        <v>12656</v>
       </c>
       <c r="N25">
-        <v>8406</v>
+        <v>12550</v>
       </c>
       <c r="O25">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -3645,57 +3717,57 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V25">
         <v>36.86</v>
       </c>
       <c r="W25" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="X25" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Y25" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="Z25" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2">
         <v>46086</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F26" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G26" t="s">
         <v>31</v>
       </c>
       <c r="H26" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I26" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J26" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K26" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L26" t="s">
         <v>36</v>
@@ -3704,13 +3776,13 @@
         <v>37803</v>
       </c>
       <c r="N26">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="O26">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="P26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -3725,72 +3797,72 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="V26">
         <v>29.4</v>
       </c>
       <c r="W26" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="X26" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Y26" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="Z26" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>46086</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F27" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G27" t="s">
         <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="I27" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J27" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="K27" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="L27" t="s">
         <v>36</v>
       </c>
       <c r="M27">
-        <v>18525</v>
+        <v>12656</v>
       </c>
       <c r="N27">
-        <v>18525</v>
+        <v>12550</v>
       </c>
       <c r="O27">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="P27" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -3805,72 +3877,72 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="V27">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W27" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="X27" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="Y27" t="s">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="Z27" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2">
         <v>46086</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F28" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="G28" t="s">
         <v>31</v>
       </c>
       <c r="H28" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I28" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J28" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="K28" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L28" t="s">
         <v>36</v>
       </c>
       <c r="M28">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N28">
-        <v>37803</v>
+        <v>18499</v>
       </c>
       <c r="O28">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="P28" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -3885,57 +3957,57 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="V28">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W28" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="X28" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="Y28" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="Z28" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B29" s="2">
         <v>46086</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G29" t="s">
         <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I29" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J29" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K29" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L29" t="s">
         <v>36</v>
@@ -3944,13 +4016,13 @@
         <v>37803</v>
       </c>
       <c r="N29">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="O29">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -3965,72 +4037,72 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="V29">
         <v>29.4</v>
       </c>
       <c r="W29" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="X29" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Y29" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="Z29" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2">
         <v>46086</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G30" t="s">
         <v>31</v>
       </c>
       <c r="H30" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J30" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="K30" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L30" t="s">
         <v>36</v>
       </c>
       <c r="M30">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N30">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O30">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -4045,72 +4117,72 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="V30">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W30" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="X30" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="Y30" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Z30" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B31" s="2">
         <v>46086</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F31" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G31" t="s">
         <v>31</v>
       </c>
       <c r="H31" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="I31" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J31" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="K31" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="L31" t="s">
         <v>36</v>
       </c>
       <c r="M31">
-        <v>18525</v>
+        <v>12656</v>
       </c>
       <c r="N31">
-        <v>18525</v>
+        <v>12550</v>
       </c>
       <c r="O31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P31" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -4125,36 +4197,36 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W31" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="X31" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="Y31" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="Z31" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B32" s="2">
         <v>46086</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
         <v>164</v>
@@ -4166,16 +4238,16 @@
         <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I32" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J32" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K32" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L32" t="s">
         <v>36</v>
@@ -4184,13 +4256,13 @@
         <v>37803</v>
       </c>
       <c r="N32">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="O32">
         <v>140</v>
       </c>
       <c r="P32" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4217,30 +4289,30 @@
         <v>167</v>
       </c>
       <c r="Y32" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="Z32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B33" s="2">
         <v>46086</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G33" t="s">
         <v>31</v>
@@ -4252,7 +4324,7 @@
         <v>33</v>
       </c>
       <c r="J33" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="K33" t="s">
         <v>35</v>
@@ -4261,16 +4333,16 @@
         <v>36</v>
       </c>
       <c r="M33">
-        <v>1794</v>
+        <v>18525</v>
       </c>
       <c r="N33">
-        <v>1777</v>
+        <v>18499</v>
       </c>
       <c r="O33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -4285,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>57.33</v>
+        <v>47.46</v>
       </c>
       <c r="W33" t="s">
         <v>172</v>
@@ -4297,60 +4369,60 @@
         <v>173</v>
       </c>
       <c r="Y33" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="Z33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B34" s="2">
         <v>46086</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
         <v>31</v>
       </c>
       <c r="H34" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J34" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="K34" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L34" t="s">
         <v>36</v>
       </c>
       <c r="M34">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N34">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O34">
-        <v>195</v>
+        <v>70</v>
       </c>
       <c r="P34" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -4365,10 +4437,10 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>195</v>
+        <v>70</v>
       </c>
       <c r="V34">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W34" t="s">
         <v>172</v>
@@ -4377,60 +4449,60 @@
         <v>173</v>
       </c>
       <c r="Y34" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="Z34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B35" s="2">
         <v>46086</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G35" t="s">
         <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J35" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="K35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L35" t="s">
         <v>36</v>
       </c>
       <c r="M35">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N35">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O35">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="P35" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -4445,72 +4517,72 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="V35">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="X35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y35" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="Z35" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B36" s="2">
         <v>46086</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F36" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G36" t="s">
         <v>31</v>
       </c>
       <c r="H36" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I36" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J36" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="K36" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L36" t="s">
         <v>36</v>
       </c>
       <c r="M36">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N36">
-        <v>37803</v>
+        <v>18499</v>
       </c>
       <c r="O36">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="P36" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -4525,57 +4597,57 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="V36">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W36" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="X36" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Y36" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="Z36" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2">
         <v>46086</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F37" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G37" t="s">
         <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I37" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J37" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="K37" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L37" t="s">
         <v>36</v>
@@ -4584,13 +4656,13 @@
         <v>18525</v>
       </c>
       <c r="N37">
-        <v>18525</v>
+        <v>18499</v>
       </c>
       <c r="O37">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P37" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -4605,57 +4677,57 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>47.46</v>
       </c>
       <c r="W37" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="X37" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="Y37" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="Z37" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B38" s="2">
         <v>46086</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="G38" t="s">
         <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I38" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J38" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K38" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L38" t="s">
         <v>36</v>
@@ -4664,13 +4736,13 @@
         <v>37803</v>
       </c>
       <c r="N38">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="O38">
         <v>140</v>
       </c>
       <c r="P38" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -4691,66 +4763,66 @@
         <v>29.4</v>
       </c>
       <c r="W38" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X38" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="Y38" t="s">
         <v>36</v>
       </c>
       <c r="Z38" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B39" s="2">
         <v>46086</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F39" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G39" t="s">
         <v>31</v>
       </c>
       <c r="H39" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="I39" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="J39" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="K39" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="L39" t="s">
         <v>36</v>
       </c>
       <c r="M39">
-        <v>37803</v>
+        <v>1791</v>
       </c>
       <c r="N39">
-        <v>37803</v>
+        <v>1777</v>
       </c>
       <c r="O39">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="P39" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -4765,72 +4837,72 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W39" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="X39" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="Y39" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="Z39" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B40" s="2">
         <v>46086</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E40" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F40" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G40" t="s">
         <v>31</v>
       </c>
       <c r="H40" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I40" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J40" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="K40" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L40" t="s">
         <v>36</v>
       </c>
       <c r="M40">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N40">
-        <v>37803</v>
+        <v>18499</v>
       </c>
       <c r="O40">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="P40" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -4845,72 +4917,72 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="V40">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W40" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="X40" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Y40" t="s">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="Z40" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B41" s="2">
         <v>46086</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E41" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G41" t="s">
         <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I41" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="J41" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="K41" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="L41" t="s">
         <v>36</v>
       </c>
       <c r="M41">
-        <v>8456</v>
+        <v>18525</v>
       </c>
       <c r="N41">
-        <v>8406</v>
+        <v>18499</v>
       </c>
       <c r="O41">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="P41" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -4925,57 +4997,57 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="V41">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W41" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="X41" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Y41" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="Z41" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B42" s="2">
         <v>46086</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E42" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G42" t="s">
         <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I42" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J42" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K42" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L42" t="s">
         <v>36</v>
@@ -4984,13 +5056,13 @@
         <v>37803</v>
       </c>
       <c r="N42">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="O42">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="P42" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -5005,72 +5077,72 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="V42">
         <v>29.4</v>
       </c>
       <c r="W42" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="X42" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Y42" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="Z42" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B43" s="2">
         <v>46086</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F43" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G43" t="s">
         <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I43" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="J43" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="K43" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="L43" t="s">
         <v>36</v>
       </c>
       <c r="M43">
-        <v>8456</v>
+        <v>18525</v>
       </c>
       <c r="N43">
-        <v>8406</v>
+        <v>18499</v>
       </c>
       <c r="O43">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="P43" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -5085,72 +5157,72 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="V43">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W43" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="X43" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y43" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B44" s="2">
         <v>46086</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G44" t="s">
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I44" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J44" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="K44" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L44" t="s">
         <v>36</v>
       </c>
       <c r="M44">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N44">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O44">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="P44" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -5165,72 +5237,72 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="V44">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W44" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="X44" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Y44" t="s">
-        <v>217</v>
+        <v>36</v>
       </c>
       <c r="Z44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B45" s="2">
         <v>46086</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G45" t="s">
         <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I45" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J45" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="K45" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L45" t="s">
         <v>36</v>
       </c>
       <c r="M45">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N45">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="O45">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="P45" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -5245,72 +5317,72 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="V45">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W45" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="X45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y45" t="s">
-        <v>47</v>
+        <v>186</v>
       </c>
       <c r="Z45" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B46" s="2">
         <v>46086</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E46" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F46" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="G46" t="s">
         <v>31</v>
       </c>
       <c r="H46" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I46" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="J46" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="K46" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L46" t="s">
         <v>36</v>
       </c>
       <c r="M46">
-        <v>8456</v>
+        <v>37803</v>
       </c>
       <c r="N46">
-        <v>8406</v>
+        <v>37748</v>
       </c>
       <c r="O46">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="P46" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -5325,72 +5397,72 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="V46">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W46" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="X46" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Y46" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="Z46" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B47" s="2">
         <v>46086</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E47" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F47" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="G47" t="s">
         <v>31</v>
       </c>
       <c r="H47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I47" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J47" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="K47" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L47" t="s">
         <v>36</v>
       </c>
       <c r="M47">
-        <v>37803</v>
+        <v>12656</v>
       </c>
       <c r="N47">
-        <v>37803</v>
+        <v>12550</v>
       </c>
       <c r="O47">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="P47" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -5405,72 +5477,72 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="V47">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W47" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="X47" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="Y47" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="Z47" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B48" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>28</v>
       </c>
       <c r="E48" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F48" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G48" t="s">
         <v>31</v>
       </c>
       <c r="H48" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="J48" t="s">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="K48" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="L48" t="s">
         <v>36</v>
       </c>
       <c r="M48">
-        <v>1794</v>
+        <v>37803</v>
       </c>
       <c r="N48">
-        <v>1777</v>
+        <v>37748</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P48" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -5485,72 +5557,72 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="V48">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W48" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="X48" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Y48" t="s">
-        <v>231</v>
+        <v>62</v>
       </c>
       <c r="Z48" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B49" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>234</v>
+        <v>28</v>
       </c>
       <c r="E49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G49" t="s">
         <v>31</v>
       </c>
       <c r="H49" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I49" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J49" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="K49" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L49" t="s">
         <v>36</v>
       </c>
       <c r="M49">
-        <v>8456</v>
+        <v>12656</v>
       </c>
       <c r="N49">
-        <v>8406</v>
+        <v>12550</v>
       </c>
       <c r="O49">
-        <v>1400</v>
+        <v>70</v>
       </c>
       <c r="P49" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -5565,42 +5637,42 @@
         <v>0</v>
       </c>
       <c r="U49">
-        <v>1400</v>
+        <v>70</v>
       </c>
       <c r="V49">
-        <v>29.7</v>
+        <v>36.86</v>
       </c>
       <c r="W49" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="X49" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y49" t="s">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="Z49" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>240</v>
+        <v>26</v>
       </c>
       <c r="B50" s="2">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="C50" t="s">
-        <v>241</v>
+        <v>27</v>
       </c>
       <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="s">
         <v>242</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>243</v>
-      </c>
-      <c r="F50" t="s">
-        <v>244</v>
       </c>
       <c r="G50" t="s">
         <v>31</v>
@@ -5612,7 +5684,7 @@
         <v>33</v>
       </c>
       <c r="J50" t="s">
-        <v>245</v>
+        <v>34</v>
       </c>
       <c r="K50" t="s">
         <v>35</v>
@@ -5621,16 +5693,16 @@
         <v>36</v>
       </c>
       <c r="M50">
-        <v>1794</v>
+        <v>18525</v>
       </c>
       <c r="N50">
-        <v>1777</v>
+        <v>18499</v>
       </c>
       <c r="O50">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="P50" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -5645,42 +5717,42 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="V50">
-        <v>57</v>
+        <v>47.46</v>
       </c>
       <c r="W50" t="s">
+        <v>244</v>
+      </c>
+      <c r="X50" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y50" t="s">
         <v>246</v>
       </c>
-      <c r="X50" t="s">
+      <c r="Z50" t="s">
         <v>247</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B51" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="C51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" t="s">
+        <v>248</v>
+      </c>
+      <c r="F51" t="s">
         <v>249</v>
-      </c>
-      <c r="D51" t="s">
-        <v>250</v>
-      </c>
-      <c r="E51" t="s">
-        <v>251</v>
-      </c>
-      <c r="F51" t="s">
-        <v>252</v>
       </c>
       <c r="G51" t="s">
         <v>31</v>
@@ -5701,46 +5773,526 @@
         <v>36</v>
       </c>
       <c r="M51">
-        <v>1794</v>
+        <v>18525</v>
       </c>
       <c r="N51">
+        <v>18499</v>
+      </c>
+      <c r="O51">
+        <v>130</v>
+      </c>
+      <c r="P51" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>130</v>
+      </c>
+      <c r="V51">
+        <v>47.46</v>
+      </c>
+      <c r="W51" t="s">
+        <v>250</v>
+      </c>
+      <c r="X51" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" t="s">
+        <v>248</v>
+      </c>
+      <c r="F52" t="s">
+        <v>249</v>
+      </c>
+      <c r="G52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" t="s">
+        <v>72</v>
+      </c>
+      <c r="I52" t="s">
+        <v>73</v>
+      </c>
+      <c r="J52" t="s">
+        <v>107</v>
+      </c>
+      <c r="K52" t="s">
+        <v>75</v>
+      </c>
+      <c r="L52" t="s">
+        <v>36</v>
+      </c>
+      <c r="M52">
+        <v>12656</v>
+      </c>
+      <c r="N52">
+        <v>12550</v>
+      </c>
+      <c r="O52">
+        <v>51</v>
+      </c>
+      <c r="P52" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>51</v>
+      </c>
+      <c r="V52">
+        <v>36.86</v>
+      </c>
+      <c r="W52" t="s">
+        <v>250</v>
+      </c>
+      <c r="X52" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C53" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E53" t="s">
+        <v>248</v>
+      </c>
+      <c r="F53" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" t="s">
+        <v>31</v>
+      </c>
+      <c r="H53" t="s">
+        <v>56</v>
+      </c>
+      <c r="I53" t="s">
+        <v>57</v>
+      </c>
+      <c r="J53" t="s">
+        <v>108</v>
+      </c>
+      <c r="K53" t="s">
+        <v>59</v>
+      </c>
+      <c r="L53" t="s">
+        <v>36</v>
+      </c>
+      <c r="M53">
+        <v>37803</v>
+      </c>
+      <c r="N53">
+        <v>37748</v>
+      </c>
+      <c r="O53">
+        <v>8</v>
+      </c>
+      <c r="P53" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>8</v>
+      </c>
+      <c r="V53">
+        <v>29.4</v>
+      </c>
+      <c r="W53" t="s">
+        <v>250</v>
+      </c>
+      <c r="X53" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C54" t="s">
+        <v>253</v>
+      </c>
+      <c r="D54" t="s">
+        <v>254</v>
+      </c>
+      <c r="E54" t="s">
+        <v>255</v>
+      </c>
+      <c r="F54" t="s">
+        <v>256</v>
+      </c>
+      <c r="G54" t="s">
+        <v>31</v>
+      </c>
+      <c r="H54" t="s">
+        <v>46</v>
+      </c>
+      <c r="I54" t="s">
+        <v>47</v>
+      </c>
+      <c r="J54" t="s">
+        <v>257</v>
+      </c>
+      <c r="K54" t="s">
+        <v>48</v>
+      </c>
+      <c r="L54" t="s">
+        <v>36</v>
+      </c>
+      <c r="M54">
+        <v>1791</v>
+      </c>
+      <c r="N54">
         <v>1777</v>
       </c>
-      <c r="O51">
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="P54" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>1</v>
+      </c>
+      <c r="V54">
+        <v>57.33</v>
+      </c>
+      <c r="W54" t="s">
+        <v>258</v>
+      </c>
+      <c r="X54" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>260</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C55" t="s">
+        <v>262</v>
+      </c>
+      <c r="D55" t="s">
+        <v>263</v>
+      </c>
+      <c r="E55" t="s">
+        <v>264</v>
+      </c>
+      <c r="F55" t="s">
+        <v>265</v>
+      </c>
+      <c r="G55" t="s">
+        <v>31</v>
+      </c>
+      <c r="H55" t="s">
+        <v>72</v>
+      </c>
+      <c r="I55" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" t="s">
+        <v>37</v>
+      </c>
+      <c r="K55" t="s">
+        <v>75</v>
+      </c>
+      <c r="L55" t="s">
+        <v>36</v>
+      </c>
+      <c r="M55">
+        <v>12656</v>
+      </c>
+      <c r="N55">
+        <v>12550</v>
+      </c>
+      <c r="O55">
+        <v>1400</v>
+      </c>
+      <c r="P55" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>1400</v>
+      </c>
+      <c r="V55">
+        <v>29.7</v>
+      </c>
+      <c r="W55" t="s">
+        <v>266</v>
+      </c>
+      <c r="X55" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>269</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C56" t="s">
+        <v>270</v>
+      </c>
+      <c r="D56" t="s">
+        <v>271</v>
+      </c>
+      <c r="E56" t="s">
+        <v>272</v>
+      </c>
+      <c r="F56" t="s">
+        <v>273</v>
+      </c>
+      <c r="G56" t="s">
+        <v>31</v>
+      </c>
+      <c r="H56" t="s">
+        <v>46</v>
+      </c>
+      <c r="I56" t="s">
+        <v>47</v>
+      </c>
+      <c r="J56" t="s">
+        <v>274</v>
+      </c>
+      <c r="K56" t="s">
+        <v>48</v>
+      </c>
+      <c r="L56" t="s">
+        <v>36</v>
+      </c>
+      <c r="M56">
+        <v>1791</v>
+      </c>
+      <c r="N56">
+        <v>1777</v>
+      </c>
+      <c r="O56">
+        <v>3</v>
+      </c>
+      <c r="P56" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>3</v>
+      </c>
+      <c r="V56">
+        <v>57</v>
+      </c>
+      <c r="W56" t="s">
+        <v>275</v>
+      </c>
+      <c r="X56" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46083</v>
+      </c>
+      <c r="C57" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F57" t="s">
+        <v>279</v>
+      </c>
+      <c r="G57" t="s">
+        <v>31</v>
+      </c>
+      <c r="H57" t="s">
+        <v>46</v>
+      </c>
+      <c r="I57" t="s">
+        <v>47</v>
+      </c>
+      <c r="J57" t="s">
+        <v>37</v>
+      </c>
+      <c r="K57" t="s">
+        <v>48</v>
+      </c>
+      <c r="L57" t="s">
+        <v>36</v>
+      </c>
+      <c r="M57">
+        <v>1791</v>
+      </c>
+      <c r="N57">
+        <v>1777</v>
+      </c>
+      <c r="O57">
         <v>6</v>
       </c>
-      <c r="P51" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
+      <c r="P57" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
         <v>6</v>
       </c>
-      <c r="V51">
+      <c r="V57">
         <v>57.33</v>
       </c>
-      <c r="W51" t="s">
-        <v>253</v>
-      </c>
-      <c r="X51" t="s">
-        <v>254</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>255</v>
+      <c r="W57" t="s">
+        <v>49</v>
+      </c>
+      <c r="X57" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
